--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amedeloitte-my.sharepoint.com/personal/ritwichatterjee_deloitte_com/Documents/Desktop/SAP Assessment Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E90854E9-3B04-4FBA-90F0-76CB91019839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDF84394-787C-4B24-B8E1-C52A5B4E7374}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E90854E9-3B04-4FBA-90F0-76CB91019839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E52224C2-5E0A-4A1E-96A4-E918F33012B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2B194D51-A276-444F-BEB8-1EF57CE1E639}"/>
   </bookViews>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>Table Name</t>
-  </si>
-  <si>
     <t>BKPF</t>
   </si>
   <si>
@@ -104,14 +101,17 @@
     <t>Billing Document: Header Data</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>TABLENAME</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,13 +119,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -140,8 +153,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,91 +500,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
